--- a/data/trans_dic/IP2004-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP2004-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores a los que les sangran las encías</t>
+          <t>Menores a los que les sangran las encías (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,42 +717,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,5; 8,56</t>
+          <t>1,53; 9,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 8,13</t>
+          <t>0,89; 8,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,0</t>
+          <t>0,0; 7,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,51</t>
+          <t>0,0; 4,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,1</t>
+          <t>0,0; 3,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,98</t>
+          <t>0,0; 3,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 5,65</t>
+          <t>0,92; 6,05</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -761,17 +762,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,24</t>
+          <t>0,45; 4,25</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,7</t>
+          <t>0,0; 3,62</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,64</t>
+          <t>0,66; 3,58</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,08; 9,18</t>
+          <t>1,08; 9,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,76; 6,41</t>
+          <t>0,77; 6,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 5,98</t>
+          <t>0,64; 6,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,35</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,01</t>
+          <t>0,0; 4,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,12</t>
+          <t>0,0; 3,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,13</t>
+          <t>0,0; 5,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 5,01</t>
+          <t>0,91; 5,34</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,41</t>
+          <t>0,38; 3,59</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,95</t>
+          <t>0,31; 3,22</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,23</t>
+          <t>0,0; 3,25</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,83</t>
+          <t>0,62; 6,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,5</t>
+          <t>0,0; 7,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,85</t>
+          <t>0,0; 6,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 5,6</t>
+          <t>0,68; 5,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,8</t>
+          <t>0,0; 6,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,72</t>
+          <t>0,0; 5,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,44</t>
+          <t>0,41; 3,36</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 4,81</t>
+          <t>0,78; 4,92</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,2</t>
+          <t>0,0; 3,36</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,4</t>
+          <t>0,0; 4,7</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,32</t>
+          <t>0,69; 4,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,57</t>
+          <t>0,73; 4,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 6,72</t>
+          <t>2,11; 6,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,21; 3,26</t>
+          <t>0,18; 2,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,97; 6,96</t>
+          <t>2,09; 6,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,95; 4,79</t>
+          <t>0,94; 4,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 4,22</t>
+          <t>0,68; 4,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 4,14</t>
+          <t>0,74; 4,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,67; 4,45</t>
+          <t>1,83; 4,61</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,77</t>
+          <t>1,22; 3,72</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,65; 4,46</t>
+          <t>1,61; 4,55</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,85</t>
+          <t>0,57; 2,75</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,3; 8,39</t>
+          <t>1,29; 7,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,37; 8,59</t>
+          <t>2,34; 8,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,25; 6,26</t>
+          <t>1,24; 6,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,67; 5,44</t>
+          <t>0,52; 5,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,16; 10,3</t>
+          <t>3,24; 10,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,65; 9,86</t>
+          <t>2,65; 9,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,01; 8,23</t>
+          <t>1,99; 7,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,98; 6,19</t>
+          <t>0,89; 6,57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,0; 7,65</t>
+          <t>3,17; 7,99</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,1; 7,69</t>
+          <t>3,1; 7,57</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,09; 5,96</t>
+          <t>2,0; 5,73</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,11; 4,66</t>
+          <t>1,21; 4,84</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,91; 7,96</t>
+          <t>0,86; 8,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,94</t>
+          <t>0,0; 9,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,6</t>
+          <t>0,0; 5,57</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,6</t>
+          <t>0,0; 10,06</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,98</t>
+          <t>0,0; 7,05</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,34</t>
+          <t>0,0; 4,46</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,09</t>
+          <t>0,0; 5,32</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,16</t>
+          <t>0,0; 10,44</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,95; 5,48</t>
+          <t>0,95; 5,61</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,5; 5,17</t>
+          <t>0,51; 4,63</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,34</t>
+          <t>0,0; 3,83</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,85; 7,18</t>
+          <t>0,87; 6,76</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,79; 4,07</t>
+          <t>1,84; 3,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,96; 4,2</t>
+          <t>1,95; 4,21</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,76; 4,24</t>
+          <t>1,78; 4,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,11</t>
+          <t>0,6; 2,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,05</t>
+          <t>2,0; 3,92</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,32</t>
+          <t>1,4; 3,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,63</t>
+          <t>0,88; 2,5</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,3</t>
+          <t>1,39; 3,32</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,13; 3,72</t>
+          <t>2,17; 3,71</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,84; 3,36</t>
+          <t>1,95; 3,38</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,53; 2,95</t>
+          <t>1,55; 2,95</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,47</t>
+          <t>1,14; 2,44</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores a los que les sangran las encías (tasa de respuesta: 99,68%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>3773</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2314</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>3335</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>3773</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2939</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>1813</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>4027</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1470; 8811</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>744; 6938</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5481</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4131</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3160</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3576</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1254; 8231</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1460; 8291</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>749; 7060</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>0; 6060</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>1577; 8571</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>3172</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2040</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2249</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1618</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>3819</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2671</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2249</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>1618</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>879; 7673</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>664; 5538</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>617; 6624</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3814</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3170</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5037</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1477; 8712</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>673; 6413</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>620; 6515</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0; 6104</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1932</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1243</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>755</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2054</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1547</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>2054</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>3479</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>1243</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>1304</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>502; 5422</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4340</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3450</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>663; 5573</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5149</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3349</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>663; 5444</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1272; 8043</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4344</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5309</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>3784</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4237</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>8110</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>7365</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>4577</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3779</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>4113</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>11149</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>8813</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>11889</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>6135</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>1313; 8089</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1383; 8327</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>4387; 13855</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>382; 5746</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>3917; 12948</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1968; 9083</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1377; 9418</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1583; 9351</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>6929; 17462</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>4884; 14881</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>6609; 18710</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>2425; 11740</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>3864</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>6437</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>3977</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2565</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>6959</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>7025</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>5567</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>4278</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>10823</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>13462</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>9544</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>6843</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>1279; 7789</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>3234; 11713</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1629; 8426</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>607; 6691</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3896; 12650</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>3475; 12320</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>2685; 10596</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>1418; 10483</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>6974; 17578</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>8350; 20382</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>5313; 15250</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>3347; 13411</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>2414</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1497</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1616</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1321</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>690</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2195</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>3735</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>1307</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>3811</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>616; 6085</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4925</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3159</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0; 6934</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4636</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3061</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3461</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 7354</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>1298; 7704</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>606; 5493</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4665</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>1208; 9424</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>17006</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>18457</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>17296</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>7651</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>18347</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>15011</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>10749</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>16087</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>35353</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>33467</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>28045</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>23738</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>11126; 24067</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>12266; 26522</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>11184; 25490</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>3898; 13637</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>12870; 25277</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>9358; 22829</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>5877; 16709</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>10245; 24437</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>27075; 46364</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>25206; 43835</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>20164; 38323</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>15770; 33793</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP2004-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP2004-Clase-trans_dic.xlsx
@@ -717,22 +717,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,53; 9,19</t>
+          <t>1,53; 8,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 8,33</t>
+          <t>0,89; 8,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,09</t>
+          <t>0,0; 6,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,0</t>
+          <t>0,0; 3,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,37 +742,37 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,82</t>
+          <t>0,0; 3,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,97</t>
+          <t>0,0; 3,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,92; 6,05</t>
+          <t>0,8; 5,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,78; 4,42</t>
+          <t>0,78; 4,48</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,25</t>
+          <t>0,45; 4,08</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,62</t>
+          <t>0,0; 3,47</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,58</t>
+          <t>0,65; 3,92</t>
         </is>
       </c>
     </row>
@@ -857,17 +857,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,08; 9,41</t>
+          <t>1,09; 9,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,77; 6,38</t>
+          <t>0,76; 6,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 6,83</t>
+          <t>0,64; 6,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,68</t>
+          <t>0,0; 3,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,44</t>
+          <t>0,0; 4,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -892,27 +892,27 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,4</t>
+          <t>0,0; 5,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,91; 5,34</t>
+          <t>0,79; 5,03</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,59</t>
+          <t>0,37; 3,71</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,22</t>
+          <t>0,31; 3,0</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,25</t>
+          <t>0,0; 3,57</t>
         </is>
       </c>
     </row>
@@ -1002,27 +1002,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 6,67</t>
+          <t>0,62; 7,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,42</t>
+          <t>0,0; 7,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,91</t>
+          <t>0,0; 7,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 5,7</t>
+          <t>0,68; 6,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,26</t>
+          <t>0,0; 6,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,27 +1032,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,3</t>
+          <t>0,0; 4,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,36</t>
+          <t>0,41; 3,47</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 4,92</t>
+          <t>0,79; 4,72</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,36</t>
+          <t>0,0; 3,81</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,7</t>
+          <t>0,0; 4,1</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,22</t>
+          <t>0,68; 4,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,39</t>
+          <t>0,78; 4,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,11; 6,67</t>
+          <t>2,08; 6,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 2,69</t>
+          <t>0,19; 2,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,09; 6,92</t>
+          <t>2,11; 6,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,94; 4,33</t>
+          <t>0,94; 4,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 4,64</t>
+          <t>0,67; 4,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 4,4</t>
+          <t>0,66; 4,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,83; 4,61</t>
+          <t>1,79; 4,76</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,72</t>
+          <t>1,27; 3,78</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,61; 4,55</t>
+          <t>1,67; 4,77</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,75</t>
+          <t>0,63; 2,82</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,29; 7,83</t>
+          <t>1,35; 7,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,34; 8,46</t>
+          <t>2,29; 8,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,24; 6,44</t>
+          <t>1,24; 6,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,52; 5,7</t>
+          <t>0,52; 5,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,24; 10,51</t>
+          <t>2,92; 10,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,65; 9,41</t>
+          <t>2,33; 9,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,99; 7,84</t>
+          <t>1,96; 7,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 6,57</t>
+          <t>0,81; 6,05</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,17; 7,99</t>
+          <t>3,0; 7,71</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,1; 7,57</t>
+          <t>3,17; 7,73</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,0; 5,73</t>
+          <t>2,05; 5,92</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,84</t>
+          <t>1,28; 4,93</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,86; 8,51</t>
+          <t>0,91; 8,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,87</t>
+          <t>0,0; 9,72</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,57</t>
+          <t>0,0; 5,52</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,06</t>
+          <t>0,0; 9,32</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,05</t>
+          <t>0,0; 6,07</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,46</t>
+          <t>0,0; 4,5</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,32</t>
+          <t>0,0; 6,42</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,44</t>
+          <t>0,0; 10,59</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,95; 5,61</t>
+          <t>0,94; 5,89</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,63</t>
+          <t>0,51; 5,09</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,83</t>
+          <t>0,0; 3,47</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,87; 6,76</t>
+          <t>0,64; 6,76</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,84; 3,98</t>
+          <t>1,81; 4,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,95; 4,21</t>
+          <t>1,9; 4,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,78; 4,06</t>
+          <t>1,81; 4,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,1</t>
+          <t>0,59; 2,19</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,0; 3,92</t>
+          <t>1,97; 4,08</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,42</t>
+          <t>1,42; 3,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,5</t>
+          <t>0,91; 2,65</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,39; 3,32</t>
+          <t>1,4; 3,39</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,17; 3,71</t>
+          <t>2,1; 3,66</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,95; 3,38</t>
+          <t>1,87; 3,3</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,55; 2,95</t>
+          <t>1,58; 2,88</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,14; 2,44</t>
+          <t>1,17; 2,47</t>
         </is>
       </c>
     </row>
@@ -1927,22 +1927,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1470; 8811</t>
+          <t>1465; 8506</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>744; 6938</t>
+          <t>740; 6682</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5481</t>
+          <t>0; 4673</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4131</t>
+          <t>0; 4007</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1952,37 +1952,37 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3160</t>
+          <t>0; 3144</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3576</t>
+          <t>0; 3360</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1254; 8231</t>
+          <t>1095; 7272</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1460; 8291</t>
+          <t>1462; 8395</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>749; 7060</t>
+          <t>750; 6779</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 6060</t>
+          <t>0; 5809</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1577; 8571</t>
+          <t>1566; 9384</t>
         </is>
       </c>
     </row>
@@ -2135,17 +2135,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>879; 7673</t>
+          <t>889; 7445</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>664; 5538</t>
+          <t>659; 5428</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>617; 6624</t>
+          <t>617; 6542</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3814</t>
+          <t>0; 3220</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3170</t>
+          <t>0; 4230</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -2170,27 +2170,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 5037</t>
+          <t>0; 5356</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1477; 8712</t>
+          <t>1291; 8200</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>673; 6413</t>
+          <t>667; 6630</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>620; 6515</t>
+          <t>620; 6070</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 6104</t>
+          <t>0; 6713</t>
         </is>
       </c>
     </row>
@@ -2348,27 +2348,27 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>502; 5422</t>
+          <t>504; 6119</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4340</t>
+          <t>0; 4590</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3450</t>
+          <t>0; 3938</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>663; 5573</t>
+          <t>666; 6121</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 5149</t>
+          <t>0; 5244</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2378,27 +2378,27 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3349</t>
+          <t>0; 3023</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>663; 5444</t>
+          <t>662; 5618</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1272; 8043</t>
+          <t>1284; 7718</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 4344</t>
+          <t>0; 4932</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 5309</t>
+          <t>0; 4633</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1313; 8089</t>
+          <t>1297; 8167</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1383; 8327</t>
+          <t>1472; 8590</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4387; 13855</t>
+          <t>4311; 14182</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>382; 5746</t>
+          <t>407; 5907</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3917; 12948</t>
+          <t>3945; 12359</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1968; 9083</t>
+          <t>1967; 9320</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1377; 9418</t>
+          <t>1352; 8593</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1583; 9351</t>
+          <t>1396; 8845</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6929; 17462</t>
+          <t>6793; 18015</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4884; 14881</t>
+          <t>5062; 15096</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6609; 18710</t>
+          <t>6852; 19597</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2425; 11740</t>
+          <t>2692; 12013</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1279; 7789</t>
+          <t>1342; 7829</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3234; 11713</t>
+          <t>3174; 11318</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1629; 8426</t>
+          <t>1626; 8621</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>607; 6691</t>
+          <t>607; 6715</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3896; 12650</t>
+          <t>3514; 12148</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3475; 12320</t>
+          <t>3054; 12129</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2685; 10596</t>
+          <t>2648; 10453</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1418; 10483</t>
+          <t>1297; 9646</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6974; 17578</t>
+          <t>6589; 16960</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8350; 20382</t>
+          <t>8552; 20813</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5313; 15250</t>
+          <t>5444; 15750</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3347; 13411</t>
+          <t>3531; 13652</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>616; 6085</t>
+          <t>653; 6153</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4925</t>
+          <t>0; 4849</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 3159</t>
+          <t>0; 3131</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 6934</t>
+          <t>0; 6419</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 4636</t>
+          <t>0; 3989</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 3061</t>
+          <t>0; 3088</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 3461</t>
+          <t>0; 4171</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 7354</t>
+          <t>0; 7458</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1298; 7704</t>
+          <t>1286; 8080</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>606; 5493</t>
+          <t>604; 6037</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 4665</t>
+          <t>0; 4217</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1208; 9424</t>
+          <t>890; 9421</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>11126; 24067</t>
+          <t>10952; 24482</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>12266; 26522</t>
+          <t>11937; 27283</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11184; 25490</t>
+          <t>11388; 25427</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3898; 13637</t>
+          <t>3836; 14180</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>12870; 25277</t>
+          <t>12700; 26282</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9358; 22829</t>
+          <t>9477; 22718</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5877; 16709</t>
+          <t>6068; 17764</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>10245; 24437</t>
+          <t>10292; 24957</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>27075; 46364</t>
+          <t>26258; 45732</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>25206; 43835</t>
+          <t>24235; 42785</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>20164; 38323</t>
+          <t>20493; 37315</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>15770; 33793</t>
+          <t>16151; 34145</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP2004-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP2004-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,44 +649,44 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2,38%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>3,94%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2,78%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>1,42%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0,76%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2,01%</t>
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,53; 8,87</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 8,02</t>
+          <t>0,0; 5,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,05</t>
+          <t>0,0; 3,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,88</t>
+          <t>0,88; 5,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,5; 8,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,8</t>
+          <t>0,88; 8,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,73</t>
+          <t>0,0; 7,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 5,34</t>
+          <t>0,0; 3,91</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,78; 4,48</t>
+          <t>0,78; 4,42</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,08</t>
+          <t>0,45; 4,24</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,47</t>
+          <t>0,0; 3,7</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,92</t>
+          <t>0,64; 3,61</t>
         </is>
       </c>
     </row>
@@ -789,62 +789,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>3,89%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>2,35%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>2,32%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>0,8%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2,34%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,09; 9,13</t>
+          <t>0,0; 4,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,76; 6,26</t>
+          <t>0,0; 4,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 6,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
+          <t>0,0; 6,32</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,08; 9,18</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,76; 6,41</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0,63; 5,98</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,95</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,59</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,74</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 5,03</t>
+          <t>0,8; 5,01</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,71</t>
+          <t>0,37; 3,41</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,0</t>
+          <t>0,3; 2,95</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,57</t>
+          <t>0,0; 3,42</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,88%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2,38%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2,13%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>0,68; 5,6</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 5,8</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,62; 7,53</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,85</t>
-        </is>
-      </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,89</t>
+          <t>0,0; 4,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 6,26</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,37</t>
+          <t>0,0; 5,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 7,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,79</t>
+          <t>0,0; 8,45</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,47</t>
+          <t>0,41; 3,44</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 4,72</t>
+          <t>0,72; 4,81</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,81</t>
+          <t>0,0; 3,2</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,1</t>
+          <t>0,0; 4,61</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3,94%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2,18%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>1,97%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2,23%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>3,9%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,94%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,18%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 4,26</t>
+          <t>1,97; 6,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 4,53</t>
+          <t>0,95; 4,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,08; 6,83</t>
+          <t>0,61; 4,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 2,76</t>
+          <t>0,74; 4,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,11; 6,61</t>
+          <t>0,69; 4,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,94; 4,44</t>
+          <t>0,76; 4,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 4,23</t>
+          <t>2,1; 6,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,66; 4,16</t>
+          <t>0,21; 4,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,79; 4,76</t>
+          <t>1,67; 4,45</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,27; 3,78</t>
+          <t>1,19; 3,77</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,67; 4,77</t>
+          <t>1,65; 4,46</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,82</t>
+          <t>0,76; 3,28</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>5,78%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5,37%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4,12%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2,79%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>3,88%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>4,65%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>3,04%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>5,78%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,37%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>4,12%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 7,87</t>
+          <t>3,16; 10,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,29; 8,17</t>
+          <t>2,65; 9,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,24; 6,59</t>
+          <t>2,01; 8,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,52; 5,72</t>
+          <t>0,94; 6,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,92; 10,09</t>
+          <t>1,3; 8,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,33; 9,26</t>
+          <t>2,37; 8,59</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,96; 7,74</t>
+          <t>1,25; 6,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,81; 6,05</t>
+          <t>0,76; 5,79</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,0; 7,71</t>
+          <t>3,0; 7,65</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,17; 7,73</t>
+          <t>3,1; 7,69</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,05; 5,92</t>
+          <t>2,09; 5,96</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,28; 4,93</t>
+          <t>1,18; 4,93</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>3,37%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>3,0%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>1,09%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2,35%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2,01%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,91; 8,6</t>
+          <t>0,0; 6,98</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,72</t>
+          <t>0,0; 5,34</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,52</t>
+          <t>0,0; 6,09</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,32</t>
+          <t>0,0; 7,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,07</t>
+          <t>0,91; 7,96</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,5</t>
+          <t>0,0; 8,94</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,42</t>
+          <t>0,0; 5,6</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,59</t>
+          <t>0,0; 9,06</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,94; 5,89</t>
+          <t>0,95; 5,48</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,51; 5,09</t>
+          <t>0,5; 5,17</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,47</t>
+          <t>0,0; 3,34</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,64; 6,76</t>
+          <t>0,66; 6,28</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2,85%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>2,82%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>2,93%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>2,75%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,85%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,81; 4,05</t>
+          <t>1,91; 4,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,33</t>
+          <t>1,37; 3,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,81; 4,05</t>
+          <t>0,9; 2,63</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,19</t>
+          <t>1,32; 3,3</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,97; 4,08</t>
+          <t>1,79; 4,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,41</t>
+          <t>1,96; 4,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,65</t>
+          <t>1,76; 4,24</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,39</t>
+          <t>0,63; 2,31</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,1; 3,66</t>
+          <t>2,13; 3,72</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,87; 3,3</t>
+          <t>1,84; 3,36</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,58; 2,88</t>
+          <t>1,53; 2,95</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,47</t>
+          <t>1,19; 2,51</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,42 +1791,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2907</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>3773</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>2314</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>1099</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>692</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>625</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3335</t>
+          <t>771</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4027</t>
+          <t>3678</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1465; 8506</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>740; 6682</t>
+          <t>0; 4215</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4673</t>
+          <t>0; 3586</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4007</t>
+          <t>1069; 6898</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1439; 8209</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3144</t>
+          <t>735; 6774</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3360</t>
+          <t>0; 5410</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1095; 7272</t>
+          <t>0; 3988</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1462; 8395</t>
+          <t>1461; 8296</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>750; 6779</t>
+          <t>748; 7031</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 5809</t>
+          <t>0; 6190</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1566; 9384</t>
+          <t>1438; 8086</t>
         </is>
       </c>
     </row>
@@ -1999,42 +1999,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,44 +2067,44 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1484</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>3172</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2040</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2249</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>630</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1618</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
           <t>3819</t>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>1484</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>889; 7445</t>
+          <t>0; 3268</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>659; 5428</t>
+          <t>0; 3794</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>617; 6542</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
+          <t>0; 5657</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>881; 7487</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>660; 5561</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>615; 5803</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0; 3220</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0; 4230</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>0; 5356</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1291; 8200</t>
+          <t>1297; 8159</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>667; 6630</t>
+          <t>666; 6091</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>620; 6070</t>
+          <t>614; 5979</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 6713</t>
+          <t>0; 6373</t>
         </is>
       </c>
     </row>
@@ -2207,37 +2207,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -2275,49 +2275,49 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2054</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1547</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>1932</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>1243</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>755</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>827</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>2054</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1547</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>549</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>2054</t>
-        </is>
-      </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
           <t>3479</t>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>1282</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>669; 5476</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4770</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>504; 6119</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0; 4590</t>
-        </is>
-      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3938</t>
+          <t>0; 2498</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>666; 6121</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 5244</t>
+          <t>0; 4737</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4385</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3023</t>
+          <t>0; 4353</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>662; 5618</t>
+          <t>664; 5559</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1284; 7718</t>
+          <t>1180; 7865</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 4932</t>
+          <t>0; 4141</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 4633</t>
+          <t>0; 4976</t>
         </is>
       </c>
     </row>
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>7365</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4577</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3779</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4234</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>3784</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>4237</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>8110</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>7365</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>4577</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3779</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>4113</t>
+          <t>2116</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>6351</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1297; 8167</t>
+          <t>3678; 13024</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1472; 8590</t>
+          <t>2000; 10061</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4311; 14182</t>
+          <t>1233; 8574</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>407; 5907</t>
+          <t>1465; 9128</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3945; 12359</t>
+          <t>1330; 8276</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1967; 9320</t>
+          <t>1432; 8675</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1352; 8593</t>
+          <t>4356; 13960</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1396; 8845</t>
+          <t>376; 7456</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6793; 18015</t>
+          <t>6342; 16868</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5062; 15096</t>
+          <t>4752; 15074</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6852; 19597</t>
+          <t>6765; 18335</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2692; 12013</t>
+          <t>2827; 12229</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>6959</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>7025</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>5567</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>4066</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>3864</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>6437</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>3977</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2565</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>6959</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>7025</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>5567</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4278</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6843</t>
+          <t>6711</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1342; 7829</t>
+          <t>3802; 12402</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3174; 11318</t>
+          <t>3463; 12909</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1626; 8621</t>
+          <t>2716; 11114</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>607; 6715</t>
+          <t>1372; 9271</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3514; 12148</t>
+          <t>1292; 8351</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3054; 12129</t>
+          <t>3275; 11892</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2648; 10453</t>
+          <t>1638; 8197</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1297; 9646</t>
+          <t>894; 6770</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6589; 16960</t>
+          <t>6587; 16820</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8552; 20813</t>
+          <t>8364; 20722</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5444; 15750</t>
+          <t>5561; 15866</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3531; 13652</t>
+          <t>3098; 12947</t>
         </is>
       </c>
     </row>
@@ -2831,32 +2831,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1321</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>690</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1538</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>2414</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>1497</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>617</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1616</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>1321</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>690</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>1595</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3811</t>
+          <t>3133</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>653; 6153</t>
+          <t>0; 4590</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4849</t>
+          <t>0; 3666</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 3131</t>
+          <t>0; 3956</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 6419</t>
+          <t>0; 4962</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 3989</t>
+          <t>649; 5695</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 3088</t>
+          <t>0; 4461</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 4171</t>
+          <t>0; 3174</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 7458</t>
+          <t>0; 6374</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1286; 8080</t>
+          <t>1304; 7519</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>604; 6037</t>
+          <t>598; 6131</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 4217</t>
+          <t>0; 4068</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>890; 9421</t>
+          <t>903; 8625</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>18347</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>15011</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>10749</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>14684</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>17006</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>18457</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>17296</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>7651</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>18347</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>15011</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>10749</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>16087</t>
+          <t>7955</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>23738</t>
+          <t>22639</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>10952; 24482</t>
+          <t>12325; 26088</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>11937; 27283</t>
+          <t>9106; 22162</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11388; 25427</t>
+          <t>6054; 17613</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3836; 14180</t>
+          <t>8939; 22382</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>12700; 26282</t>
+          <t>10824; 24579</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9477; 22718</t>
+          <t>12318; 26414</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6068; 17764</t>
+          <t>11031; 26626</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>10292; 24957</t>
+          <t>3866; 14150</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>26258; 45732</t>
+          <t>26618; 46406</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>24235; 42785</t>
+          <t>23863; 43502</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>20493; 37315</t>
+          <t>19818; 38339</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>16151; 34145</t>
+          <t>15360; 32446</t>
         </is>
       </c>
     </row>
